--- a/excel_reports/backtest_compare/s18/compare_s18_M5_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s18/compare_s18_M5_20260528_0800_20260608_1000.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 10:57:31</t>
+          <t>2026-06-19 09:51:24</t>
         </is>
       </c>
     </row>
